--- a/badcase.xlsx
+++ b/badcase.xlsx
@@ -1,31 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\develop\full-duplex\qwen3-tts\badcase\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\26034\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41ECFEC2-6C64-4897-AD9B-0255BD988C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C8C539D-C289-4A3A-93CA-34752CCEC3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60420" yWindow="16095" windowWidth="29970" windowHeight="18105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="195" yWindow="2295" windowWidth="30480" windowHeight="17685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="125725"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="67">
   <si>
     <t>咳血、盗汗、低热持续月余，肺结核可能性较大，但需靠检查确诊。请尽快做痰检和胸部CT，别自行判断用药。</t>
   </si>
@@ -36,9 +31,6 @@
     <t>避免劳累，保持室内通风，不要吸烟，饮食清淡多喝水，注意休息，避免传染他人，尽快就医明确诊断。</t>
   </si>
   <si>
-    <t>左肺占位伴少量胸腔积液，需警惕肿瘤或结核可能，建议尽快做胸水检查和占位穿刺活检，明确病因。</t>
-  </si>
-  <si>
     <t>无便血但下腹痛持续，仍需警惕盆腔炎、泌尿系结石或肠道问题，建议尽快做腹部B超明确病因。</t>
   </si>
   <si>
@@ -69,17 +61,7 @@
     <t>重度OSA合并心脑血管病，CPAP依从差，需评估上气道解剖结构。若鼻中隔偏曲或扁桃体肥大明显，可考虑手术矫正。您有鼻塞或打鼾加重吗？</t>
   </si>
   <si>
-    <t>意识障碍需用GCS和CSS评估。促醒可试促醒药物、高压氧、经颅磁刺激。康复需早期介入，结合理疗、言语训练。您患者昏迷多久了？</t>
-  </si>
-  <si>
-    <t>华法林患者补钙和维生素D安全，但维生素K2需谨慎。建议选钙剂+维生素D3，每日钙600mg，维生素D3 800IU。维生素K2不建议额外补充，以免影响华法林效果。您妈妈目前INR值是多少？</t>
-  </si>
-  <si>
     <t>“和痰找”播报韵律比较奇怪</t>
-  </si>
-  <si>
-    <t>“咳”字发音有误
-“持续--月余”中间有不自然停顿</t>
   </si>
   <si>
     <t>播报到“加做”时有卡顿，不清晰</t>
@@ -113,16 +95,6 @@
     <t>“滥用”发音有误</t>
   </si>
   <si>
-    <t>“10.8 mmol/L”发音有误</t>
-  </si>
-  <si>
-    <t>“10.8”发音有误</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> “ mmol/L   ”发音有误
-语速过慢</t>
-  </si>
-  <si>
     <t>“监测INR”中间有长时间停顿</t>
   </si>
   <si>
@@ -155,14 +127,8 @@
     <t>正确</t>
   </si>
   <si>
-    <t>尿液浑浊伴尿检错误、夜尿多，提示可能有尿路感染或结石，建议尽快做尿培养和泌尿系B超。</t>
-  </si>
-  <si>
     <t>“错误”发音有杂音
 语速过慢</t>
-  </si>
-  <si>
-    <t>利伐沙班无需常规监测INR。它属于直接口服抗凝药，作用稳定，一般不需像华法林那样频繁查凝血。您目前有出血或错误症状吗？</t>
   </si>
   <si>
     <r>
@@ -172,6 +138,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="等线"/>
+        <charset val="134"/>
       </rPr>
       <t>和</t>
     </r>
@@ -180,6 +147,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="等线"/>
+        <charset val="134"/>
       </rPr>
       <t>痰找抗酸杆菌检查</t>
     </r>
@@ -188,6 +156,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <charset val="134"/>
       </rPr>
       <t>，别耽误。</t>
     </r>
@@ -197,6 +166,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="等线"/>
+        <charset val="134"/>
       </rPr>
       <t>紫癜</t>
     </r>
@@ -205,6 +175,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <charset val="134"/>
       </rPr>
       <t>性肾炎激素无效，提示病情较重，需肾穿刺明确分型。若为Ⅲ级以上，建议加用免疫抑制剂。您孩子蛋白尿程度是？</t>
     </r>
@@ -228,33 +199,127 @@
 RefAudio 10s</t>
   </si>
   <si>
+    <t>10.8 mmol/L, 二甲双胍读法错误
+断句停顿错误</t>
+  </si>
+  <si>
+    <t>___ 读法错误
+断句停顿错误</t>
+  </si>
+  <si>
+    <t>依从差读法错误
+断句停顿错误</t>
+  </si>
+  <si>
+    <t>阿福</t>
+  </si>
+  <si>
+    <t>阿里百炼 Qwen-TTS-Realtime</t>
+  </si>
+  <si>
+    <t>正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左肺占位伴少量胸腔积液，需警惕肿瘤或结核可能，建议尽快做胸水检查和占位穿刺活检，明确病因。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尿液浑浊伴尿检异常、夜尿多，提示可能有尿路感染或结石，建议尽快做尿培养和泌尿系B超。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>读法错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>利伐沙班无需常规监测INR。它属于直接口服抗凝药，作用稳定，一般不需像华法林那样频繁查凝血。您目前有出血或异常症状吗？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“痰找抗酸杆菌检查”读法错误？停顿错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“咳”字发音有误
+“持续--月余”中间有不自然停顿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“咳”字发音有误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“10.8 mmol/L”发音有误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“10.8”发音有误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> “ mmol/L   ”发音有误
+语速过慢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> “ mmol/L   ”发音有误，后半句话丢失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断句停顿错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>意识障碍需用GCS和CSS评估。促醒可试促醒药物、高压氧、经颅磁刺激。康复需早期介入，结合理疗、言语训练。您患者昏迷多久了？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“高压氧、经颅磁刺激”断句停顿错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>“8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>00”读法错误</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>“痰找抗酸杆菌检查”读法错误
 断句停顿错误</t>
-  </si>
-  <si>
-    <t>10.8 mmol/L, 二甲双胍读法错误
-断句停顿错误</t>
-  </si>
-  <si>
-    <t>___ 读法错误
-断句停顿错误</t>
-  </si>
-  <si>
-    <t>依从差读法错误
-断句停顿错误</t>
-  </si>
-  <si>
-    <t>阿福</t>
-  </si>
-  <si>
-    <t>阿里百炼 Qwen-TTS-Realtime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“备注”停顿错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“GCS”读成“GCC”，语速过快</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>华法林患者补钙和维生素D安全，但维生素K2需谨慎。建议选钙剂+维生素D3，每日钙600mg，维生素D3 800IU。维生素K2不建议额外补充，以免影响华法林效果。您妈妈目前INR值是多少？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“D3 800IU”读法错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
@@ -271,26 +336,51 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -321,52 +411,58 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -669,430 +765,564 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultColWidth="34.68359375" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="34.625" defaultRowHeight="15.75" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.3671875" style="9" customWidth="1"/>
-    <col min="2" max="2" width="61.68359375" style="7" customWidth="1"/>
-    <col min="3" max="4" width="35.734375" style="7" customWidth="1"/>
-    <col min="5" max="5" width="35.62890625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="24.1015625" style="11" customWidth="1"/>
-    <col min="7" max="8" width="25.47265625" style="11" customWidth="1"/>
-    <col min="9" max="16384" width="34.68359375" style="7"/>
+    <col min="1" max="1" width="6.375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="61.625" style="7" customWidth="1"/>
+    <col min="3" max="4" width="35.75" style="7" customWidth="1"/>
+    <col min="5" max="5" width="35.625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="24.125" style="11" customWidth="1"/>
+    <col min="7" max="8" width="25.5" style="11" customWidth="1"/>
+    <col min="9" max="16384" width="34.625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="3" customFormat="1" ht="33.299999999999997" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" s="3" customFormat="1" ht="33.4" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="47.25" x14ac:dyDescent="0.15">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
+        <v>34</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>46</v>
+      </c>
       <c r="E2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>50</v>
+        <v>13</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>62</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.4">
+        <v>37</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="31.5" x14ac:dyDescent="0.15">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="6" t="s">
-        <v>17</v>
+      <c r="C3" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>52</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="31.5" x14ac:dyDescent="0.15">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>46</v>
+      </c>
       <c r="E4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.4">
+        <v>14</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="31.5" x14ac:dyDescent="0.15">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>46</v>
+      </c>
       <c r="E5" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="31.5" x14ac:dyDescent="0.15">
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="B6" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>46</v>
+      </c>
       <c r="E6" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="31.5" x14ac:dyDescent="0.15">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+        <v>3</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>46</v>
+      </c>
       <c r="E7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.4">
+        <v>17</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="31.5" x14ac:dyDescent="0.15">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>46</v>
+      </c>
       <c r="E8" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="31.5" x14ac:dyDescent="0.15">
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="B9" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>46</v>
+      </c>
       <c r="E9" s="6" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="30" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="31.5" x14ac:dyDescent="0.15">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>46</v>
+      </c>
       <c r="E10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>39</v>
+        <v>19</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="45" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="31.5" x14ac:dyDescent="0.15">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>46</v>
+      </c>
       <c r="E11" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="31.5" x14ac:dyDescent="0.15">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+        <v>7</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>46</v>
+      </c>
       <c r="E12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.4">
+        <v>21</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="31.5" x14ac:dyDescent="0.15">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+        <v>8</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>46</v>
+      </c>
       <c r="E13" s="6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="45" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="31.5" x14ac:dyDescent="0.15">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="6" t="s">
-        <v>27</v>
+        <v>9</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>54</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="45" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="47.25" x14ac:dyDescent="0.15">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6" t="s">
-        <v>28</v>
+        <v>10</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>55</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="45" x14ac:dyDescent="0.4">
+        <v>41</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="31.5" x14ac:dyDescent="0.15">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="6" t="s">
-        <v>29</v>
+        <v>11</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>56</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="45" x14ac:dyDescent="0.4">
+        <v>42</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="31.5" x14ac:dyDescent="0.15">
       <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+      <c r="B17" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>46</v>
+      </c>
       <c r="E17" s="6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="31.5" x14ac:dyDescent="0.15">
       <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
+        <v>35</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>46</v>
+      </c>
       <c r="E18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.4">
+      <c r="G18" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="47.25" x14ac:dyDescent="0.15">
       <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>46</v>
+      </c>
       <c r="E19" s="6" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="45" x14ac:dyDescent="0.4">
+        <v>43</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="31.5" x14ac:dyDescent="0.15">
       <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
+      <c r="B20" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>60</v>
+      </c>
       <c r="E20" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="60" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="47.25" x14ac:dyDescent="0.15">
       <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
+      <c r="B21" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>61</v>
+      </c>
       <c r="E21" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A22" s="4"/>
     </row>
   </sheetData>
